--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/lib-gral-bdo-o-higgins.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/lib-gral-bdo-o-higgins.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>19236.99</v>
+        <v>19022.66</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>42607.59</v>
+        <v>42056.86</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>31425.63</v>
+        <v>31112.96</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>25082.71</v>
+        <v>24833.15</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>19069.53</v>
+        <v>19120.1</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>37677.46</v>
+        <v>37777.37</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>37677.46</v>
+        <v>37883.5</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>71218.82000000001</v>
+        <v>70974.39999999999</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>21662.27</v>
+        <v>21587.92</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>15309.04</v>
+        <v>15409.86</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>31520.15</v>
+        <v>31348.5</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>37571.1</v>
+        <v>37349.69</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>38478.13</v>
+        <v>37921.46</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>22710.59</v>
+        <v>22182.13</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>21857.2</v>
+        <v>22148.18</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>64614.03</v>
+        <v>64961.98</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>21054.26</v>
+        <v>21001.1</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>27015.92</v>
+        <v>27148.63</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>14338.52</v>
+        <v>14384.16</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>38791.81</v>
+        <v>38998.09</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>39425.33</v>
+        <v>40092.11</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>22987.66</v>
+        <v>22671.8</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>37416.03</v>
+        <v>37771.44</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>29858.07</v>
+        <v>29376.24</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>597.45</v>
+        <v>587.8099999999999</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>41386.51</v>
+        <v>40718.63</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>1119.35</v>
+        <v>1101.28</v>
       </c>
     </row>
   </sheetData>
